--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -42,6 +42,15 @@
   </si>
   <si>
     <t>SPL</t>
+  </si>
+  <si>
+    <t>HRD0834</t>
+  </si>
+  <si>
+    <t>HRD0835</t>
+  </si>
+  <si>
+    <t>HRD0920</t>
   </si>
 </sst>
 </file>
@@ -690,7 +699,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1230,14 +1239,14 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
+      <c r="A2" t="s" s="0">
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -38,19 +38,13 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>GWP0001</t>
+    <t>GWP0052</t>
   </si>
   <si>
     <t>SPL</t>
   </si>
   <si>
-    <t>HRD0834</t>
-  </si>
-  <si>
-    <t>HRD0835</t>
-  </si>
-  <si>
-    <t>HRD0920</t>
+    <t>GWP0106</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1234,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>GWP0106</t>
+  </si>
+  <si>
+    <t>GWP1149</t>
+  </si>
+  <si>
+    <t>GWP1150</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1240,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>GWP1150</t>
+  </si>
+  <si>
+    <t>GWP3375</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1243,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>GWP3375</t>
+  </si>
+  <si>
+    <t>GWP4675</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1246,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/testdata/EmployeeAllowanceData.xlsx
+++ b/testdata/EmployeeAllowanceData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>GWP4675</t>
+  </si>
+  <si>
+    <t>GWP5680</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1249,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
